--- a/matlabfilesuk/ch8Plots/az.xlsx
+++ b/matlabfilesuk/ch8Plots/az.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mriani\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\books\DataScienceWithMatlab\matlabMfilesUK\ch8Plots\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7AB1FA-2D32-4BF7-9B7D-6720F5FFBDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9576" tabRatio="764"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dati" sheetId="1" r:id="rId1"/>
@@ -26,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t>provincia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Barilla </t>
   </si>
   <si>
@@ -75,12 +73,15 @@
   </si>
   <si>
     <t>FATT</t>
+  </si>
+  <si>
+    <t>Firm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -110,8 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -392,273 +392,266 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Foglio1"/>
-  <dimension ref="A3:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A3:G13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.20703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4">
+        <v>-25.1</v>
+      </c>
+      <c r="C4">
+        <v>7.4</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>4.2</v>
+      </c>
+      <c r="F4">
+        <v>0.8</v>
+      </c>
+      <c r="G4">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>-140</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>69</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>65.8</v>
+      </c>
+      <c r="C6">
+        <v>9.6</v>
+      </c>
+      <c r="D6">
+        <v>54</v>
+      </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>-71</v>
+      </c>
+      <c r="C7">
+        <v>8.1</v>
+      </c>
+      <c r="D7">
+        <v>56</v>
+      </c>
+      <c r="E7">
+        <v>2.7</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>-32</v>
+      </c>
+      <c r="C8">
+        <v>5.8</v>
+      </c>
+      <c r="D8">
+        <v>72</v>
+      </c>
+      <c r="E8">
+        <v>3.2</v>
+      </c>
+      <c r="F8">
+        <v>0.4</v>
+      </c>
+      <c r="G8">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>-28</v>
+      </c>
+      <c r="C9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D9">
+        <v>39</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>-92</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>81</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1.7</v>
+      </c>
+      <c r="G10">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>-145</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>37</v>
+      </c>
+      <c r="E11">
+        <v>2.1</v>
+      </c>
+      <c r="F11">
+        <v>5.9</v>
+      </c>
+      <c r="G11">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>31</v>
+      </c>
+      <c r="C12">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>25</v>
+      </c>
+      <c r="F12">
+        <v>1.5</v>
+      </c>
+      <c r="G12">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>63</v>
+      </c>
+      <c r="E13">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1">
-        <v>-25.1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>7.4</v>
-      </c>
-      <c r="D4" s="1">
-        <v>60</v>
-      </c>
-      <c r="E4" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2867</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1">
-        <v>-140</v>
-      </c>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="1">
-        <v>69</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1">
-        <v>65.8</v>
-      </c>
-      <c r="C6" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="D6" s="1">
-        <v>54</v>
-      </c>
-      <c r="E6" s="1">
-        <v>21</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="F13">
         <v>0</v>
       </c>
-      <c r="G6" s="1">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1">
-        <v>-71</v>
-      </c>
-      <c r="C7" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>56</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2.7</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1">
-        <v>-32</v>
-      </c>
-      <c r="C8" s="1">
-        <v>5.8</v>
-      </c>
-      <c r="D8" s="1">
-        <v>72</v>
-      </c>
-      <c r="E8" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1">
-        <v>-28</v>
-      </c>
-      <c r="C9" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="D9" s="1">
-        <v>39</v>
-      </c>
-      <c r="E9" s="1">
-        <v>5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1">
-        <v>-92</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1">
-        <v>81</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="G10" s="1">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1">
-        <v>-145</v>
-      </c>
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1">
-        <v>37</v>
-      </c>
-      <c r="E11" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1">
-        <v>31</v>
-      </c>
-      <c r="C12" s="1">
-        <v>28</v>
-      </c>
-      <c r="D12" s="1">
-        <v>32</v>
-      </c>
-      <c r="E12" s="1">
-        <v>25</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="G12" s="1">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1">
-        <v>7</v>
-      </c>
-      <c r="D13" s="1">
-        <v>63</v>
-      </c>
-      <c r="E13" s="1">
-        <v>11</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="G13">
         <v>820</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
